--- a/events/LaSeu_2021_WC/LaSeu_2021_WC_start.xlsx
+++ b/events/LaSeu_2021_WC/LaSeu_2021_WC_start.xlsx
@@ -24131,6 +24131,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X409" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -33147,6 +33152,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -37109,6 +37119,11 @@
       <c r="R619" t="inlineStr">
         <is>
           <t>FISEROVA Tereza</t>
+        </is>
+      </c>
+      <c r="X619" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
     </row>
